--- a/Workshops/Jan_2026_Online/Kilauea.xlsx
+++ b/Workshops/Jan_2026_Online/Kilauea.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\penny\Box\Berkeley_new\Conferences\GSA2024\MELTScourse\Activity 2\Activity 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gleesonm/Library/CloudStorage/GoogleDrive-gleesonm@berkeley.edu/My Drive/2022/GitHub/PetThermoTools/Workshops/Jan_2026_Online/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F1F5E9-3B1F-4CFC-BAC7-02E9840F7F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4157C6-6098-3848-9154-512E06F00EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{269F38A2-D933-6C4D-B6F9-B0341D7D6E9D}"/>
+    <workbookView xWindow="28800" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{269F38A2-D933-6C4D-B6F9-B0341D7D6E9D}"/>
   </bookViews>
   <sheets>
     <sheet name="Matrix Glass" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="352">
   <si>
     <t>Sample number</t>
   </si>
@@ -567,21 +567,6 @@
   </si>
   <si>
     <t>LL2_417</t>
-  </si>
-  <si>
-    <t>LL11_507 no sims</t>
-  </si>
-  <si>
-    <t>LL8_405_nosims</t>
-  </si>
-  <si>
-    <t>LL8_403_nosims</t>
-  </si>
-  <si>
-    <t>LL7_275_a_nosims</t>
-  </si>
-  <si>
-    <t>LL7_275_b_nosims</t>
   </si>
   <si>
     <t>H2O_Liq</t>
@@ -1206,7 +1191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1218,7 +1203,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1578,9 +1562,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9052D420-AF8C-DF48-954B-87B0A36C81C6}">
   <dimension ref="A1:N266"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="32" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,7 +1608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1668,7 +1652,7 @@
         <v>98.000299999999996</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1712,7 +1696,7 @@
         <v>96.463700000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1756,7 +1740,7 @@
         <v>98.587500000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1800,7 +1784,7 @@
         <v>98.590500000000006</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1844,7 +1828,7 @@
         <v>99.375299999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1888,7 +1872,7 @@
         <v>99.754499999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1932,7 +1916,7 @@
         <v>99.157700000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1976,7 +1960,7 @@
         <v>99.223200000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -2020,7 +2004,7 @@
         <v>98.648799999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -2064,7 +2048,7 @@
         <v>98.200100000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +2092,7 @@
         <v>98.165199999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -2152,7 +2136,7 @@
         <v>97.561400000000006</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -2196,7 +2180,7 @@
         <v>97.369</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2240,7 +2224,7 @@
         <v>98.650700000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2284,7 +2268,7 @@
         <v>98.471699999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -2328,7 +2312,7 @@
         <v>98.675600000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2372,7 +2356,7 @@
         <v>98.051699999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -2416,7 +2400,7 @@
         <v>96.650400000000005</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -2460,7 +2444,7 @@
         <v>97.652799999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -2504,7 +2488,7 @@
         <v>97.324600000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -2548,7 +2532,7 @@
         <v>98.402900000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -2592,7 +2576,7 @@
         <v>97.86375000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -2636,7 +2620,7 @@
         <v>97.611699999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -2680,7 +2664,7 @@
         <v>97.083699999999993</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -2724,7 +2708,7 @@
         <v>98.021799999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -2768,7 +2752,7 @@
         <v>97.751400000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -2812,7 +2796,7 @@
         <v>97.886600000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -2856,7 +2840,7 @@
         <v>98.407600000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -2900,7 +2884,7 @@
         <v>97.6755</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -2944,7 +2928,7 @@
         <v>97.1541</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -2988,7 +2972,7 @@
         <v>96.549000000000007</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -3032,7 +3016,7 @@
         <v>97.190799999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -3076,7 +3060,7 @@
         <v>96.869900000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -3120,7 +3104,7 @@
         <v>97.013400000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -3164,7 +3148,7 @@
         <v>97.502099999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -3208,7 +3192,7 @@
         <v>97.516199999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -3252,7 +3236,7 @@
         <v>97.832999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -3296,7 +3280,7 @@
         <v>97.844999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -3340,7 +3324,7 @@
         <v>97.263800000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -3384,7 +3368,7 @@
         <v>97.554400000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -3428,7 +3412,7 @@
         <v>98.232200000000006</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -3472,7 +3456,7 @@
         <v>97.630200000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -3516,7 +3500,7 @@
         <v>98.309799999999996</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -3560,7 +3544,7 @@
         <v>97.97</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -3604,7 +3588,7 @@
         <v>98.694400000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -3648,7 +3632,7 @@
         <v>98.509299999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -3692,7 +3676,7 @@
         <v>98.601849999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -3736,7 +3720,7 @@
         <v>98.233999999999995</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -3780,7 +3764,7 @@
         <v>98.412599999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -3824,7 +3808,7 @@
         <v>98.323299999999989</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -3868,7 +3852,7 @@
         <v>98.877799999999993</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -3912,7 +3896,7 @@
         <v>99.233699999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -3956,7 +3940,7 @@
         <v>99.055749999999989</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -4000,7 +3984,7 @@
         <v>99.028899999999993</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -4044,7 +4028,7 @@
         <v>98.835499999999996</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -4088,7 +4072,7 @@
         <v>98.932199999999995</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -4132,7 +4116,7 @@
         <v>98.738799999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -4176,7 +4160,7 @@
         <v>97.878399999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -4220,7 +4204,7 @@
         <v>98.308599999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -4264,7 +4248,7 @@
         <v>97.678100000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -4308,7 +4292,7 @@
         <v>98.287400000000005</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -4352,7 +4336,7 @@
         <v>98.889700000000005</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -4396,7 +4380,7 @@
         <v>98.732399999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -4440,7 +4424,7 @@
         <v>98.811049999999994</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>9</v>
       </c>
@@ -4484,7 +4468,7 @@
         <v>97.461100000000002</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>9</v>
       </c>
@@ -4528,7 +4512,7 @@
         <v>98.021000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>9</v>
       </c>
@@ -4572,7 +4556,7 @@
         <v>97.163399999999996</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>9</v>
       </c>
@@ -4616,7 +4600,7 @@
         <v>97.8767</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -4660,7 +4644,7 @@
         <v>97.868899999999996</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>9</v>
       </c>
@@ -4704,7 +4688,7 @@
         <v>97.823700000000002</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>9</v>
       </c>
@@ -4748,7 +4732,7 @@
         <v>97.7624</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>9</v>
       </c>
@@ -4792,7 +4776,7 @@
         <v>97.3202</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>9</v>
       </c>
@@ -4836,7 +4820,7 @@
         <v>97.541300000000007</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>9</v>
       </c>
@@ -4880,7 +4864,7 @@
         <v>97.260499999999993</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>9</v>
       </c>
@@ -4924,7 +4908,7 @@
         <v>97.959299999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>9</v>
       </c>
@@ -4968,7 +4952,7 @@
         <v>97.609899999999996</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>9</v>
       </c>
@@ -5012,7 +4996,7 @@
         <v>97.497399999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -5056,7 +5040,7 @@
         <v>98.791399999999996</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -5100,7 +5084,7 @@
         <v>98.14439999999999</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -5144,7 +5128,7 @@
         <v>97.787000000000006</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>9</v>
       </c>
@@ -5188,7 +5172,7 @@
         <v>98.477000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>9</v>
       </c>
@@ -5232,7 +5216,7 @@
         <v>98.132000000000005</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>9</v>
       </c>
@@ -5276,7 +5260,7 @@
         <v>97.186199999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>9</v>
       </c>
@@ -5320,7 +5304,7 @@
         <v>97.855599999999995</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>9</v>
       </c>
@@ -5364,7 +5348,7 @@
         <v>97.520899999999997</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>2</v>
       </c>
@@ -5408,7 +5392,7 @@
         <v>97.393900000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>2</v>
       </c>
@@ -5452,7 +5436,7 @@
         <v>97.378100000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>2</v>
       </c>
@@ -5496,7 +5480,7 @@
         <v>98.497799999999998</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>2</v>
       </c>
@@ -5540,7 +5524,7 @@
         <v>98.103499999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>2</v>
       </c>
@@ -5584,7 +5568,7 @@
         <v>98.619299999999996</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>2</v>
       </c>
@@ -5628,7 +5612,7 @@
         <v>98.361400000000003</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>2</v>
       </c>
@@ -5672,7 +5656,7 @@
         <v>98.684600000000003</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>2</v>
       </c>
@@ -5716,7 +5700,7 @@
         <v>98.217200000000005</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>2</v>
       </c>
@@ -5760,7 +5744,7 @@
         <v>98.450900000000004</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>2</v>
       </c>
@@ -5804,7 +5788,7 @@
         <v>97.115799999999993</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -5848,7 +5832,7 @@
         <v>96.692800000000005</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>2</v>
       </c>
@@ -5892,7 +5876,7 @@
         <v>97.075500000000005</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>2</v>
       </c>
@@ -5936,7 +5920,7 @@
         <v>96.390900000000002</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>2</v>
       </c>
@@ -5980,7 +5964,7 @@
         <v>96.733200000000011</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>2</v>
       </c>
@@ -6024,7 +6008,7 @@
         <v>98.176500000000004</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>2</v>
       </c>
@@ -6068,7 +6052,7 @@
         <v>98.450599999999994</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>2</v>
       </c>
@@ -6112,7 +6096,7 @@
         <v>98.313549999999992</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>8</v>
       </c>
@@ -6156,7 +6140,7 @@
         <v>97.820499999999996</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>8</v>
       </c>
@@ -6200,7 +6184,7 @@
         <v>97.645300000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>8</v>
       </c>
@@ -6244,7 +6228,7 @@
         <v>97.732900000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>8</v>
       </c>
@@ -6288,7 +6272,7 @@
         <v>98.660600000000002</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>8</v>
       </c>
@@ -6332,7 +6316,7 @@
         <v>98.920400000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>8</v>
       </c>
@@ -6376,7 +6360,7 @@
         <v>98.790500000000009</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>8</v>
       </c>
@@ -6420,7 +6404,7 @@
         <v>96.703400000000002</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>8</v>
       </c>
@@ -6464,7 +6448,7 @@
         <v>97.179500000000004</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>8</v>
       </c>
@@ -6508,7 +6492,7 @@
         <v>96.941450000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -6552,7 +6536,7 @@
         <v>97.301500000000004</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>8</v>
       </c>
@@ -6596,7 +6580,7 @@
         <v>97.335300000000004</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>8</v>
       </c>
@@ -6640,7 +6624,7 @@
         <v>97.318399999999997</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>8</v>
       </c>
@@ -6684,7 +6668,7 @@
         <v>97.481399999999994</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>8</v>
       </c>
@@ -6728,7 +6712,7 @@
         <v>98.0197</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>8</v>
       </c>
@@ -6772,7 +6756,7 @@
         <v>97.750550000000004</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -6816,7 +6800,7 @@
         <v>98.070599999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -6860,7 +6844,7 @@
         <v>98.150800000000004</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -6904,7 +6888,7 @@
         <v>98.022000000000006</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -6948,7 +6932,7 @@
         <v>97.466700000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -6992,7 +6976,7 @@
         <v>98.281400000000005</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -7036,7 +7020,7 @@
         <v>98.802800000000005</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -7080,7 +7064,7 @@
         <v>98.027299999999997</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -7124,7 +7108,7 @@
         <v>99.082999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -7168,7 +7152,7 @@
         <v>98.341999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -7212,7 +7196,7 @@
         <v>97.836699999999993</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -7256,7 +7240,7 @@
         <v>98.207599999999999</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -7300,7 +7284,7 @@
         <v>98.289699999999996</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -7344,7 +7328,7 @@
         <v>98.575900000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -7388,7 +7372,7 @@
         <v>96.806200000000004</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -7432,7 +7416,7 @@
         <v>97.691050000000004</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -7476,7 +7460,7 @@
         <v>98.392799999999994</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -7520,7 +7504,7 @@
         <v>98.566999999999993</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -7564,7 +7548,7 @@
         <v>98.473200000000006</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -7608,7 +7592,7 @@
         <v>97.7744</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -7652,7 +7636,7 @@
         <v>98.123800000000003</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -7696,7 +7680,7 @@
         <v>99.185599999999994</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -7740,7 +7724,7 @@
         <v>98.493200000000002</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>3</v>
       </c>
@@ -7784,7 +7768,7 @@
         <v>97.6614</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>3</v>
       </c>
@@ -7828,7 +7812,7 @@
         <v>97.893000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>3</v>
       </c>
@@ -7872,7 +7856,7 @@
         <v>97.0946</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>3</v>
       </c>
@@ -7916,7 +7900,7 @@
         <v>96.946100000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>3</v>
       </c>
@@ -7960,7 +7944,7 @@
         <v>97.020350000000008</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>3</v>
       </c>
@@ -8004,7 +7988,7 @@
         <v>96.373900000000006</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>3</v>
       </c>
@@ -8048,7 +8032,7 @@
         <v>96.996700000000004</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>3</v>
       </c>
@@ -8092,7 +8076,7 @@
         <v>96.685300000000012</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>3</v>
       </c>
@@ -8136,7 +8120,7 @@
         <v>98.491799999999998</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>3</v>
       </c>
@@ -8180,7 +8164,7 @@
         <v>97.593299999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>3</v>
       </c>
@@ -8224,7 +8208,7 @@
         <v>98.042550000000006</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>3</v>
       </c>
@@ -8268,7 +8252,7 @@
         <v>97.580399999999997</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>3</v>
       </c>
@@ -8312,7 +8296,7 @@
         <v>97.996200000000002</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -8356,7 +8340,7 @@
         <v>97.788299999999992</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>3</v>
       </c>
@@ -8400,7 +8384,7 @@
         <v>98.253699999999995</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>3</v>
       </c>
@@ -8444,7 +8428,7 @@
         <v>99.138499999999993</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>3</v>
       </c>
@@ -8488,7 +8472,7 @@
         <v>98.696100000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>3</v>
       </c>
@@ -8532,7 +8516,7 @@
         <v>97.812399999999997</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>3</v>
       </c>
@@ -8576,7 +8560,7 @@
         <v>98.041399999999996</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>7</v>
       </c>
@@ -8620,7 +8604,7 @@
         <v>98.613299999999995</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>7</v>
       </c>
@@ -8664,7 +8648,7 @@
         <v>98.902199999999993</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>7</v>
       </c>
@@ -8708,7 +8692,7 @@
         <v>98.757749999999987</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>7</v>
       </c>
@@ -8752,7 +8736,7 @@
         <v>98.046700000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -8796,7 +8780,7 @@
         <v>98.025700000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>7</v>
       </c>
@@ -8840,7 +8824,7 @@
         <v>98.036200000000008</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>7</v>
       </c>
@@ -8884,7 +8868,7 @@
         <v>98.569199999999995</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>7</v>
       </c>
@@ -8928,7 +8912,7 @@
         <v>98.709199999999996</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -8972,7 +8956,7 @@
         <v>98.639199999999988</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>7</v>
       </c>
@@ -9016,7 +9000,7 @@
         <v>97.769599999999997</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>7</v>
       </c>
@@ -9060,7 +9044,7 @@
         <v>97.766900000000007</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>7</v>
       </c>
@@ -9104,7 +9088,7 @@
         <v>97.768249999999995</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>7</v>
       </c>
@@ -9148,7 +9132,7 @@
         <v>98.208600000000004</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>7</v>
       </c>
@@ -9192,7 +9176,7 @@
         <v>98.738699999999994</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>7</v>
       </c>
@@ -9236,7 +9220,7 @@
         <v>97.988299999999995</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>7</v>
       </c>
@@ -9280,7 +9264,7 @@
         <v>97.969899999999996</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>7</v>
       </c>
@@ -9324,7 +9308,7 @@
         <v>97.979099999999988</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>7</v>
       </c>
@@ -9368,7 +9352,7 @@
         <v>97.658299999999997</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>7</v>
       </c>
@@ -9412,7 +9396,7 @@
         <v>97.923900000000003</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>7</v>
       </c>
@@ -9456,7 +9440,7 @@
         <v>97.258799999999994</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -9500,7 +9484,7 @@
         <v>97.822599999999994</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -9544,7 +9528,7 @@
         <v>98.395799999999994</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -9588,7 +9572,7 @@
         <v>98.342600000000004</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>10</v>
       </c>
@@ -9632,7 +9616,7 @@
         <v>98.775099999999995</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -9676,7 +9660,7 @@
         <v>98.253200000000007</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>10</v>
       </c>
@@ -9720,7 +9704,7 @@
         <v>98.823999999999998</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>10</v>
       </c>
@@ -9764,7 +9748,7 @@
         <v>98.617433333333338</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>10</v>
       </c>
@@ -9808,7 +9792,7 @@
         <v>98.706999999999994</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>10</v>
       </c>
@@ -9852,7 +9836,7 @@
         <v>98.811099999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>10</v>
       </c>
@@ -9896,7 +9880,7 @@
         <v>98.839299999999994</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>10</v>
       </c>
@@ -9940,7 +9924,7 @@
         <v>98.785799999999995</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>10</v>
       </c>
@@ -9984,7 +9968,7 @@
         <v>99.089100000000002</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>10</v>
       </c>
@@ -10028,7 +10012,7 @@
         <v>99.490799999999993</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>10</v>
       </c>
@@ -10072,7 +10056,7 @@
         <v>99.289950000000005</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>10</v>
       </c>
@@ -10116,7 +10100,7 @@
         <v>97.563400000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -10160,7 +10144,7 @@
         <v>98.471199999999996</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -10204,7 +10188,7 @@
         <v>97.637500000000003</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -10248,7 +10232,7 @@
         <v>97.890699999999995</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -10292,7 +10276,7 @@
         <v>99.222999999999999</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -10336,7 +10320,7 @@
         <v>98.938599999999994</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -10380,7 +10364,7 @@
         <v>98.831400000000002</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -10424,7 +10408,7 @@
         <v>98.99766666666666</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>11</v>
       </c>
@@ -10468,7 +10452,7 @@
         <v>99.571899999999999</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>11</v>
       </c>
@@ -10512,7 +10496,7 @@
         <v>99.074799999999996</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -10556,7 +10540,7 @@
         <v>98.805400000000006</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>11</v>
       </c>
@@ -10600,7 +10584,7 @@
         <v>99.150700000000015</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>11</v>
       </c>
@@ -10644,7 +10628,7 @@
         <v>99.625</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>11</v>
       </c>
@@ -10688,7 +10672,7 @@
         <v>99.098299999999995</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>11</v>
       </c>
@@ -10732,7 +10716,7 @@
         <v>97.841999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -10776,7 +10760,7 @@
         <v>98.855099999999993</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -10820,7 +10804,7 @@
         <v>99.691100000000006</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>11</v>
       </c>
@@ -10864,7 +10848,7 @@
         <v>98.900999999999996</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>11</v>
       </c>
@@ -10908,7 +10892,7 @@
         <v>99.752399999999994</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>11</v>
       </c>
@@ -10952,7 +10936,7 @@
         <v>99.44816666666668</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>11</v>
       </c>
@@ -10996,7 +10980,7 @@
         <v>99.335999999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>11</v>
       </c>
@@ -11040,7 +11024,7 @@
         <v>97.939499999999995</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>11</v>
       </c>
@@ -11084,7 +11068,7 @@
         <v>97.501000000000005</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>11</v>
       </c>
@@ -11128,7 +11112,7 @@
         <v>98.637749999999997</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -11172,7 +11156,7 @@
         <v>99.232299999999995</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -11216,7 +11200,7 @@
         <v>99.335599999999999</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>11</v>
       </c>
@@ -11260,7 +11244,7 @@
         <v>98.4786</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -11304,7 +11288,7 @@
         <v>99.005266666666671</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -11348,7 +11332,7 @@
         <v>99.289299999999997</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>12</v>
       </c>
@@ -11392,7 +11376,7 @@
         <v>99.067400000000006</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>12</v>
       </c>
@@ -11436,7 +11420,7 @@
         <v>98.925200000000004</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>12</v>
       </c>
@@ -11480,7 +11464,7 @@
         <v>99.093966666666674</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>12</v>
       </c>
@@ -11524,7 +11508,7 @@
         <v>99.414900000000003</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>12</v>
       </c>
@@ -11568,7 +11552,7 @@
         <v>100.4653</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>12</v>
       </c>
@@ -11612,7 +11596,7 @@
         <v>99.039000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>12</v>
       </c>
@@ -11656,7 +11640,7 @@
         <v>99.639733333333325</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>12</v>
       </c>
@@ -11700,7 +11684,7 @@
         <v>99.099699999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>12</v>
       </c>
@@ -11744,7 +11728,7 @@
         <v>99.269400000000005</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>12</v>
       </c>
@@ -11788,7 +11772,7 @@
         <v>99.306399999999996</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>12</v>
       </c>
@@ -11832,7 +11816,7 @@
         <v>99.225166666666667</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>12</v>
       </c>
@@ -11876,7 +11860,7 @@
         <v>98.7911</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>12</v>
       </c>
@@ -11920,7 +11904,7 @@
         <v>98.536500000000004</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>12</v>
       </c>
@@ -11964,7 +11948,7 @@
         <v>99.3643</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>12</v>
       </c>
@@ -12008,7 +11992,7 @@
         <v>98.897300000000016</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -12052,7 +12036,7 @@
         <v>99.360500000000002</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>12</v>
       </c>
@@ -12096,7 +12080,7 @@
         <v>98.758499999999998</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>12</v>
       </c>
@@ -12140,7 +12124,7 @@
         <v>98.804299999999998</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>12</v>
       </c>
@@ -12184,7 +12168,7 @@
         <v>98.974433333333323</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>12</v>
       </c>
@@ -12228,7 +12212,7 @@
         <v>99.511200000000002</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>13</v>
       </c>
@@ -12272,7 +12256,7 @@
         <v>98.953100000000006</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>13</v>
       </c>
@@ -12316,7 +12300,7 @@
         <v>98.959900000000005</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -12360,7 +12344,7 @@
         <v>99.565399999999997</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>13</v>
       </c>
@@ -12404,7 +12388,7 @@
         <v>99.159466666666674</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>13</v>
       </c>
@@ -12448,7 +12432,7 @@
         <v>99.130600000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>13</v>
       </c>
@@ -12492,7 +12476,7 @@
         <v>98.758700000000005</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>13</v>
       </c>
@@ -12536,7 +12520,7 @@
         <v>98.491299999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>13</v>
       </c>
@@ -12580,7 +12564,7 @@
         <v>98.793533333333315</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>13</v>
       </c>
@@ -12624,7 +12608,7 @@
         <v>98.009900000000002</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>13</v>
       </c>
@@ -12668,7 +12652,7 @@
         <v>99.795900000000003</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>13</v>
       </c>
@@ -12712,7 +12696,7 @@
         <v>98.108699999999999</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>13</v>
       </c>
@@ -12756,7 +12740,7 @@
         <v>98.638166666666663</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>13</v>
       </c>
@@ -12800,7 +12784,7 @@
         <v>98.815100000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -12844,7 +12828,7 @@
         <v>98.724999999999994</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>13</v>
       </c>
@@ -12888,7 +12872,7 @@
         <v>99.005200000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>13</v>
       </c>
@@ -12932,7 +12916,7 @@
         <v>98.848433333333332</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>13</v>
       </c>
@@ -12976,7 +12960,7 @@
         <v>99.215599999999995</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>13</v>
       </c>
@@ -13020,7 +13004,7 @@
         <v>97.825800000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>13</v>
       </c>
@@ -13064,7 +13048,7 @@
         <v>97.861599999999996</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>13</v>
       </c>
@@ -13108,7 +13092,7 @@
         <v>98.301000000000002</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>13</v>
       </c>
@@ -13152,7 +13136,7 @@
         <v>99.268199999999993</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>13</v>
       </c>
@@ -13196,7 +13180,7 @@
         <v>99.065100000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>13</v>
       </c>
@@ -13240,7 +13224,7 @@
         <v>99.210700000000003</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>13</v>
       </c>
@@ -13301,14 +13285,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBE55E07-FD1B-E648-844F-CB33AC4BAF33}">
-  <dimension ref="A1:V155"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:V150"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
     <col min="12" max="13" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -13343,40 +13327,40 @@
         <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N1" t="s">
         <v>24</v>
       </c>
       <c r="O1" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="V1" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -13440,11 +13424,11 @@
       <c r="U2">
         <v>0.19134999999999999</v>
       </c>
-      <c r="V2" s="7">
+      <c r="V2">
         <v>420</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -13508,11 +13492,11 @@
       <c r="U3">
         <v>0.187</v>
       </c>
-      <c r="V3" s="7">
+      <c r="V3">
         <v>360</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -13576,11 +13560,11 @@
       <c r="U4">
         <v>0.24260000000000001</v>
       </c>
-      <c r="V4" s="7">
+      <c r="V4">
         <v>640</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -13644,11 +13628,11 @@
       <c r="U5">
         <v>0.24030000000000001</v>
       </c>
-      <c r="V5" s="7">
+      <c r="V5">
         <v>370</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -13712,11 +13696,11 @@
       <c r="U6">
         <v>0.18229999999999999</v>
       </c>
-      <c r="V6" s="7">
+      <c r="V6">
         <v>420</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -13780,11 +13764,11 @@
       <c r="U7">
         <v>0.19255</v>
       </c>
-      <c r="V7" s="7">
+      <c r="V7">
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -13848,11 +13832,11 @@
       <c r="U8">
         <v>0.17860000000000001</v>
       </c>
-      <c r="V8" s="7">
+      <c r="V8">
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -13916,11 +13900,11 @@
       <c r="U9">
         <v>0.23250000000000001</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9">
         <v>470</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -13984,11 +13968,11 @@
       <c r="U10">
         <v>0.19894999999999999</v>
       </c>
-      <c r="V10" s="7">
+      <c r="V10">
         <v>420</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -14052,11 +14036,11 @@
       <c r="U11">
         <v>0.28944999999999999</v>
       </c>
-      <c r="V11" s="7">
+      <c r="V11">
         <v>290</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -14120,11 +14104,11 @@
       <c r="U12">
         <v>0.19139999999999999</v>
       </c>
-      <c r="V12" s="7">
+      <c r="V12">
         <v>440</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -14188,11 +14172,11 @@
       <c r="U13">
         <v>0.19139999999999999</v>
       </c>
-      <c r="V13" s="7">
+      <c r="V13">
         <v>440</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -14256,11 +14240,11 @@
       <c r="U14">
         <v>0.20080000000000001</v>
       </c>
-      <c r="V14" s="7">
+      <c r="V14">
         <v>440</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -14324,11 +14308,11 @@
       <c r="U15">
         <v>0.20080000000000001</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15">
         <v>460</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -14392,11 +14376,11 @@
       <c r="U16">
         <v>0.1668</v>
       </c>
-      <c r="V16" s="7">
+      <c r="V16">
         <v>160</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -14460,11 +14444,11 @@
       <c r="U17">
         <v>0.19205</v>
       </c>
-      <c r="V17" s="7">
+      <c r="V17">
         <v>210</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -14528,11 +14512,11 @@
       <c r="U18">
         <v>0.19205</v>
       </c>
-      <c r="V18" s="7">
+      <c r="V18">
         <v>210</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -14596,11 +14580,11 @@
       <c r="U19">
         <v>0.1653</v>
       </c>
-      <c r="V19" s="7">
+      <c r="V19">
         <v>370</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -14664,11 +14648,11 @@
       <c r="U20">
         <v>0.1653</v>
       </c>
-      <c r="V20" s="7">
+      <c r="V20">
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>46</v>
       </c>
@@ -14732,11 +14716,11 @@
       <c r="U21">
         <v>0.1744</v>
       </c>
-      <c r="V21" s="7">
+      <c r="V21">
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -14800,11 +14784,11 @@
       <c r="U22">
         <v>0.17469999999999999</v>
       </c>
-      <c r="V22" s="7">
+      <c r="V22">
         <v>360</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -14868,11 +14852,11 @@
       <c r="U23">
         <v>0.17774999999999999</v>
       </c>
-      <c r="V23" s="7">
+      <c r="V23">
         <v>370</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -14936,11 +14920,11 @@
       <c r="U24">
         <v>0.17774999999999999</v>
       </c>
-      <c r="V24" s="7">
+      <c r="V24">
         <v>360</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -15004,11 +14988,11 @@
       <c r="U25">
         <v>0.18325</v>
       </c>
-      <c r="V25" s="7">
+      <c r="V25">
         <v>320</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>51</v>
       </c>
@@ -15072,11 +15056,11 @@
       <c r="U26">
         <v>0.20735000000000001</v>
       </c>
-      <c r="V26" s="7">
+      <c r="V26">
         <v>710</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -15140,11 +15124,11 @@
       <c r="U27">
         <v>0.20735000000000001</v>
       </c>
-      <c r="V27" s="7">
+      <c r="V27">
         <v>370</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -15208,11 +15192,11 @@
       <c r="U28">
         <v>0.20735000000000001</v>
       </c>
-      <c r="V28" s="7">
+      <c r="V28">
         <v>420</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -15276,11 +15260,11 @@
       <c r="U29">
         <v>0.19355</v>
       </c>
-      <c r="V29" s="7">
+      <c r="V29">
         <v>330</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>55</v>
       </c>
@@ -15344,11 +15328,11 @@
       <c r="U30">
         <v>0.18820000000000001</v>
       </c>
-      <c r="V30" s="7">
+      <c r="V30">
         <v>390</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>56</v>
       </c>
@@ -15412,11 +15396,11 @@
       <c r="U31">
         <v>0.18154999999999999</v>
       </c>
-      <c r="V31" s="7">
+      <c r="V31">
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -15480,11 +15464,11 @@
       <c r="U32">
         <v>0.18154999999999999</v>
       </c>
-      <c r="V32" s="7">
+      <c r="V32">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -15548,11 +15532,11 @@
       <c r="U33">
         <v>0.17695</v>
       </c>
-      <c r="V33" s="7">
+      <c r="V33">
         <v>410</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -15616,11 +15600,11 @@
       <c r="U34">
         <v>0.2145</v>
       </c>
-      <c r="V34" s="7">
+      <c r="V34">
         <v>280</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -15684,11 +15668,11 @@
       <c r="U35">
         <v>0.21575</v>
       </c>
-      <c r="V35" s="7">
+      <c r="V35">
         <v>360</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -15752,11 +15736,11 @@
       <c r="U36">
         <v>0.17380000000000001</v>
       </c>
-      <c r="V36" s="7">
+      <c r="V36">
         <v>280</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -15820,11 +15804,11 @@
       <c r="U37">
         <v>0.2369</v>
       </c>
-      <c r="V37" s="7">
+      <c r="V37">
         <v>470</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -15888,11 +15872,11 @@
       <c r="U38">
         <v>0.2036</v>
       </c>
-      <c r="V38" s="7">
+      <c r="V38">
         <v>460</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -15956,11 +15940,11 @@
       <c r="U39">
         <v>0.26150000000000001</v>
       </c>
-      <c r="V39" s="7">
+      <c r="V39">
         <v>440</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -16024,11 +16008,11 @@
       <c r="U40">
         <v>0.223833333333333</v>
       </c>
-      <c r="V40" s="7">
+      <c r="V40">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -16092,11 +16076,11 @@
       <c r="U41">
         <v>0.223833333333333</v>
       </c>
-      <c r="V41" s="7">
+      <c r="V41">
         <v>310</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -16160,11 +16144,11 @@
       <c r="U42">
         <v>0.223833333333333</v>
       </c>
-      <c r="V42" s="7">
+      <c r="V42">
         <v>500</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -16228,11 +16212,11 @@
       <c r="U43">
         <v>0.223833333333333</v>
       </c>
-      <c r="V43" s="7">
+      <c r="V43">
         <v>380</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>69</v>
       </c>
@@ -16296,11 +16280,11 @@
       <c r="U44">
         <v>0.42415000000000003</v>
       </c>
-      <c r="V44" s="7">
+      <c r="V44">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>70</v>
       </c>
@@ -16364,11 +16348,11 @@
       <c r="U45">
         <v>0.42415000000000003</v>
       </c>
-      <c r="V45" s="7">
+      <c r="V45">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>71</v>
       </c>
@@ -16432,11 +16416,11 @@
       <c r="U46">
         <v>0.38993333333333302</v>
       </c>
-      <c r="V46" s="7">
+      <c r="V46">
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -16500,11 +16484,11 @@
       <c r="U47">
         <v>0.38993333333333302</v>
       </c>
-      <c r="V47" s="7">
+      <c r="V47">
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>73</v>
       </c>
@@ -16568,11 +16552,11 @@
       <c r="U48">
         <v>0.39040000000000002</v>
       </c>
-      <c r="V48" s="7">
+      <c r="V48">
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -16636,11 +16620,11 @@
       <c r="U49">
         <v>0.1668</v>
       </c>
-      <c r="V49" s="7">
+      <c r="V49">
         <v>220</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -16704,11 +16688,11 @@
       <c r="U50">
         <v>0.1893</v>
       </c>
-      <c r="V50" s="7">
+      <c r="V50">
         <v>520</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -16772,11 +16756,11 @@
       <c r="U51">
         <v>0.1893</v>
       </c>
-      <c r="V51" s="7">
+      <c r="V51">
         <v>520</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -16840,11 +16824,11 @@
       <c r="U52">
         <v>0.21616666666666701</v>
       </c>
-      <c r="V52" s="7">
+      <c r="V52">
         <v>520</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -16908,11 +16892,11 @@
       <c r="U53">
         <v>0.21616666666666701</v>
       </c>
-      <c r="V53" s="7">
+      <c r="V53">
         <v>500</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -16976,11 +16960,11 @@
       <c r="U54">
         <v>0.375966666666667</v>
       </c>
-      <c r="V54" s="7">
+      <c r="V54">
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -17044,11 +17028,11 @@
       <c r="U55">
         <v>0.375966666666667</v>
       </c>
-      <c r="V55" s="7">
+      <c r="V55">
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -17112,11 +17096,11 @@
       <c r="U56">
         <v>0.33110000000000001</v>
       </c>
-      <c r="V56" s="7">
+      <c r="V56">
         <v>120</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -17180,11 +17164,11 @@
       <c r="U57">
         <v>0.22725000000000001</v>
       </c>
-      <c r="V57" s="7">
+      <c r="V57">
         <v>640</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -17248,11 +17232,11 @@
       <c r="U58">
         <v>0.25159999999999999</v>
       </c>
-      <c r="V58" s="7">
+      <c r="V58">
         <v>360</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -17316,11 +17300,11 @@
       <c r="U59">
         <v>0.2525</v>
       </c>
-      <c r="V59" s="7">
+      <c r="V59">
         <v>330</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>85</v>
       </c>
@@ -17384,11 +17368,11 @@
       <c r="U60">
         <v>0.2525</v>
       </c>
-      <c r="V60" s="7">
+      <c r="V60">
         <v>320</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>86</v>
       </c>
@@ -17452,11 +17436,11 @@
       <c r="U61">
         <v>0.21440000000000001</v>
       </c>
-      <c r="V61" s="7">
+      <c r="V61">
         <v>420</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>87</v>
       </c>
@@ -17520,11 +17504,11 @@
       <c r="U62">
         <v>0.21440000000000001</v>
       </c>
-      <c r="V62" s="7">
+      <c r="V62">
         <v>540</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>88</v>
       </c>
@@ -17588,11 +17572,11 @@
       <c r="U63">
         <v>0.16864999999999999</v>
       </c>
-      <c r="V63" s="7">
+      <c r="V63">
         <v>390</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>89</v>
       </c>
@@ -17656,11 +17640,11 @@
       <c r="U64">
         <v>0.3458</v>
       </c>
-      <c r="V64" s="7">
+      <c r="V64">
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>90</v>
       </c>
@@ -17724,11 +17708,11 @@
       <c r="U65">
         <v>0.32190000000000002</v>
       </c>
-      <c r="V65" s="7">
+      <c r="V65">
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>91</v>
       </c>
@@ -17792,11 +17776,11 @@
       <c r="U66">
         <v>0.32479999999999998</v>
       </c>
-      <c r="V66" s="7">
+      <c r="V66">
         <v>210</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>92</v>
       </c>
@@ -17860,11 +17844,11 @@
       <c r="U67">
         <v>0.32640000000000002</v>
       </c>
-      <c r="V67" s="7">
+      <c r="V67">
         <v>270</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>93</v>
       </c>
@@ -17928,11 +17912,11 @@
       <c r="U68">
         <v>0.2198</v>
       </c>
-      <c r="V68" s="7">
+      <c r="V68">
         <v>580</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>94</v>
       </c>
@@ -17996,11 +17980,11 @@
       <c r="U69">
         <v>0.18784999999999999</v>
       </c>
-      <c r="V69" s="7">
+      <c r="V69">
         <v>550</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>95</v>
       </c>
@@ -18064,11 +18048,11 @@
       <c r="U70">
         <v>0.20935000000000001</v>
       </c>
-      <c r="V70" s="7">
+      <c r="V70">
         <v>500</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>96</v>
       </c>
@@ -18132,11 +18116,11 @@
       <c r="U71">
         <v>0.27700000000000002</v>
       </c>
-      <c r="V71" s="7">
+      <c r="V71">
         <v>310</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>97</v>
       </c>
@@ -18200,11 +18184,11 @@
       <c r="U72">
         <v>0.19464999999999999</v>
       </c>
-      <c r="V72" s="7">
+      <c r="V72">
         <v>470</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>98</v>
       </c>
@@ -18268,11 +18252,11 @@
       <c r="U73">
         <v>0.18525</v>
       </c>
-      <c r="V73" s="7">
+      <c r="V73">
         <v>600</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>99</v>
       </c>
@@ -18336,11 +18320,11 @@
       <c r="U74">
         <v>0.33289999999999997</v>
       </c>
-      <c r="V74" s="7">
+      <c r="V74">
         <v>330</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>100</v>
       </c>
@@ -18404,11 +18388,11 @@
       <c r="U75">
         <v>0.40489999999999998</v>
       </c>
-      <c r="V75" s="7">
+      <c r="V75">
         <v>380</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -18472,11 +18456,11 @@
       <c r="U76">
         <v>0.39929999999999999</v>
       </c>
-      <c r="V76" s="7">
+      <c r="V76">
         <v>460</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -18540,11 +18524,11 @@
       <c r="U77">
         <v>0.36475000000000002</v>
       </c>
-      <c r="V77" s="7">
+      <c r="V77">
         <v>980</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>103</v>
       </c>
@@ -18608,11 +18592,11 @@
       <c r="U78">
         <v>0.33400000000000002</v>
       </c>
-      <c r="V78" s="7">
+      <c r="V78">
         <v>420</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>104</v>
       </c>
@@ -18676,11 +18660,11 @@
       <c r="U79">
         <v>0.39560000000000001</v>
       </c>
-      <c r="V79" s="7">
+      <c r="V79">
         <v>630</v>
       </c>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>105</v>
       </c>
@@ -18744,11 +18728,11 @@
       <c r="U80">
         <v>0.3982</v>
       </c>
-      <c r="V80" s="7">
+      <c r="V80">
         <v>610</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>106</v>
       </c>
@@ -18812,11 +18796,11 @@
       <c r="U81">
         <v>0.41454999999999997</v>
       </c>
-      <c r="V81" s="7">
+      <c r="V81">
         <v>630</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>107</v>
       </c>
@@ -18880,11 +18864,11 @@
       <c r="U82">
         <v>0.40210000000000001</v>
       </c>
-      <c r="V82" s="7">
+      <c r="V82">
         <v>1050</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>108</v>
       </c>
@@ -18948,11 +18932,11 @@
       <c r="U83">
         <v>0.23039999999999999</v>
       </c>
-      <c r="V83" s="7">
+      <c r="V83">
         <v>1020</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>109</v>
       </c>
@@ -19016,11 +19000,11 @@
       <c r="U84">
         <v>0.2392</v>
       </c>
-      <c r="V84" s="7">
+      <c r="V84">
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>110</v>
       </c>
@@ -19084,11 +19068,11 @@
       <c r="U85">
         <v>0.38555</v>
       </c>
-      <c r="V85" s="7">
+      <c r="V85">
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>111</v>
       </c>
@@ -19152,11 +19136,11 @@
       <c r="U86">
         <v>0.39550000000000002</v>
       </c>
-      <c r="V86" s="7">
+      <c r="V86">
         <v>720</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>112</v>
       </c>
@@ -19220,11 +19204,11 @@
       <c r="U87">
         <v>0.37275000000000003</v>
       </c>
-      <c r="V87" s="7">
+      <c r="V87">
         <v>560</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>113</v>
       </c>
@@ -19288,11 +19272,11 @@
       <c r="U88">
         <v>0.39784999999999998</v>
       </c>
-      <c r="V88" s="7">
+      <c r="V88">
         <v>910</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -19356,11 +19340,11 @@
       <c r="U89">
         <v>0.32140000000000002</v>
       </c>
-      <c r="V89" s="7">
+      <c r="V89">
         <v>410</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>115</v>
       </c>
@@ -19424,11 +19408,11 @@
       <c r="U90">
         <v>0.38655</v>
       </c>
-      <c r="V90" s="7">
+      <c r="V90">
         <v>810</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>116</v>
       </c>
@@ -19492,11 +19476,11 @@
       <c r="U91">
         <v>0.39379999999999998</v>
       </c>
-      <c r="V91" s="7">
+      <c r="V91">
         <v>380</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>117</v>
       </c>
@@ -19560,11 +19544,11 @@
       <c r="U92">
         <v>0.39145000000000002</v>
       </c>
-      <c r="V92" s="7">
+      <c r="V92">
         <v>450</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -19628,11 +19612,11 @@
       <c r="U93">
         <v>0.38419999999999999</v>
       </c>
-      <c r="V93" s="7">
+      <c r="V93">
         <v>690</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>119</v>
       </c>
@@ -19696,11 +19680,11 @@
       <c r="U94">
         <v>0.38829999999999998</v>
       </c>
-      <c r="V94" s="7">
+      <c r="V94">
         <v>60</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>120</v>
       </c>
@@ -19764,11 +19748,11 @@
       <c r="U95">
         <v>0.32629999999999998</v>
       </c>
-      <c r="V95" s="7">
+      <c r="V95">
         <v>450</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>121</v>
       </c>
@@ -19832,11 +19816,11 @@
       <c r="U96">
         <v>0.38924999999999998</v>
       </c>
-      <c r="V96" s="7">
+      <c r="V96">
         <v>850</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>122</v>
       </c>
@@ -19900,11 +19884,11 @@
       <c r="U97">
         <v>0.39145000000000002</v>
       </c>
-      <c r="V97" s="7">
+      <c r="V97">
         <v>660</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>123</v>
       </c>
@@ -19968,11 +19952,11 @@
       <c r="U98">
         <v>0.37069999999999997</v>
       </c>
-      <c r="V98" s="7">
+      <c r="V98">
         <v>610</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>124</v>
       </c>
@@ -20036,11 +20020,11 @@
       <c r="U99">
         <v>0.22425</v>
       </c>
-      <c r="V99" s="7">
+      <c r="V99">
         <v>370</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -20104,11 +20088,11 @@
       <c r="U100">
         <v>0.36075000000000002</v>
       </c>
-      <c r="V100" s="7">
+      <c r="V100">
         <v>760</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>126</v>
       </c>
@@ -20172,11 +20156,11 @@
       <c r="U101">
         <v>0.37664999999999998</v>
       </c>
-      <c r="V101" s="7">
+      <c r="V101">
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -20240,11 +20224,11 @@
       <c r="U102">
         <v>0.37314999999999998</v>
       </c>
-      <c r="V102" s="7">
+      <c r="V102">
         <v>60</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>128</v>
       </c>
@@ -20308,11 +20292,11 @@
       <c r="U103">
         <v>0.37695000000000001</v>
       </c>
-      <c r="V103" s="7">
+      <c r="V103">
         <v>670</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>129</v>
       </c>
@@ -20376,11 +20360,11 @@
       <c r="U104">
         <v>0.3896</v>
       </c>
-      <c r="V104" s="7">
+      <c r="V104">
         <v>700</v>
       </c>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>130</v>
       </c>
@@ -20444,11 +20428,11 @@
       <c r="U105">
         <v>0.36845</v>
       </c>
-      <c r="V105" s="7">
+      <c r="V105">
         <v>70</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>131</v>
       </c>
@@ -20512,11 +20496,11 @@
       <c r="U106">
         <v>0.38464999999999999</v>
       </c>
-      <c r="V106" s="7">
+      <c r="V106">
         <v>780</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>132</v>
       </c>
@@ -20580,11 +20564,11 @@
       <c r="U107">
         <v>0.30554999999999999</v>
       </c>
-      <c r="V107" s="7">
+      <c r="V107">
         <v>980</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>133</v>
       </c>
@@ -20648,11 +20632,11 @@
       <c r="U108">
         <v>0.29375000000000001</v>
       </c>
-      <c r="V108" s="7">
+      <c r="V108">
         <v>410</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>134</v>
       </c>
@@ -20716,11 +20700,11 @@
       <c r="U109">
         <v>0.3483</v>
       </c>
-      <c r="V109" s="7">
+      <c r="V109">
         <v>800</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>135</v>
       </c>
@@ -20784,11 +20768,11 @@
       <c r="U110">
         <v>0.37745000000000001</v>
       </c>
-      <c r="V110" s="7">
+      <c r="V110">
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>136</v>
       </c>
@@ -20852,11 +20836,11 @@
       <c r="U111">
         <v>0.30635000000000001</v>
       </c>
-      <c r="V111" s="7">
+      <c r="V111">
         <v>570</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>137</v>
       </c>
@@ -20920,11 +20904,11 @@
       <c r="U112">
         <v>0.37605</v>
       </c>
-      <c r="V112" s="7">
+      <c r="V112">
         <v>840</v>
       </c>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>138</v>
       </c>
@@ -20988,11 +20972,11 @@
       <c r="U113">
         <v>0.38705000000000001</v>
       </c>
-      <c r="V113" s="7">
+      <c r="V113">
         <v>1470</v>
       </c>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -21056,11 +21040,11 @@
       <c r="U114">
         <v>0.26300000000000001</v>
       </c>
-      <c r="V114" s="7">
+      <c r="V114">
         <v>740</v>
       </c>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>140</v>
       </c>
@@ -21124,11 +21108,11 @@
       <c r="U115">
         <v>0.38109999999999999</v>
       </c>
-      <c r="V115" s="7">
+      <c r="V115">
         <v>700</v>
       </c>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>141</v>
       </c>
@@ -21192,11 +21176,11 @@
       <c r="U116">
         <v>0.39219999999999999</v>
       </c>
-      <c r="V116" s="7">
+      <c r="V116">
         <v>920</v>
       </c>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>142</v>
       </c>
@@ -21260,11 +21244,11 @@
       <c r="U117">
         <v>0.36635000000000001</v>
       </c>
-      <c r="V117" s="7">
+      <c r="V117">
         <v>720</v>
       </c>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>143</v>
       </c>
@@ -21328,11 +21312,11 @@
       <c r="U118">
         <v>0.29380000000000001</v>
       </c>
-      <c r="V118" s="7">
+      <c r="V118">
         <v>880</v>
       </c>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>144</v>
       </c>
@@ -21396,11 +21380,11 @@
       <c r="U119">
         <v>0.38100000000000001</v>
       </c>
-      <c r="V119" s="7">
+      <c r="V119">
         <v>820</v>
       </c>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>145</v>
       </c>
@@ -21464,11 +21448,11 @@
       <c r="U120">
         <v>0.32734999999999997</v>
       </c>
-      <c r="V120" s="7">
+      <c r="V120">
         <v>920</v>
       </c>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>146</v>
       </c>
@@ -21532,11 +21516,11 @@
       <c r="U121">
         <v>0.18145</v>
       </c>
-      <c r="V121" s="7">
+      <c r="V121">
         <v>320</v>
       </c>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>147</v>
       </c>
@@ -21600,11 +21584,11 @@
       <c r="U122">
         <v>0.1757</v>
       </c>
-      <c r="V122" s="7">
+      <c r="V122">
         <v>430</v>
       </c>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>148</v>
       </c>
@@ -21668,11 +21652,11 @@
       <c r="U123">
         <v>0.40244999999999997</v>
       </c>
-      <c r="V123" s="7">
+      <c r="V123">
         <v>690</v>
       </c>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>149</v>
       </c>
@@ -21736,11 +21720,11 @@
       <c r="U124">
         <v>0.38085000000000002</v>
       </c>
-      <c r="V124" s="7">
+      <c r="V124">
         <v>360</v>
       </c>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>150</v>
       </c>
@@ -21804,11 +21788,11 @@
       <c r="U125">
         <v>0.37290000000000001</v>
       </c>
-      <c r="V125" s="7">
+      <c r="V125">
         <v>490</v>
       </c>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>151</v>
       </c>
@@ -21872,11 +21856,11 @@
       <c r="U126">
         <v>0.3705</v>
       </c>
-      <c r="V126" s="7">
+      <c r="V126">
         <v>660</v>
       </c>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>152</v>
       </c>
@@ -21940,11 +21924,11 @@
       <c r="U127">
         <v>0.38579999999999998</v>
       </c>
-      <c r="V127" s="7">
+      <c r="V127">
         <v>770</v>
       </c>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>153</v>
       </c>
@@ -22008,11 +21992,11 @@
       <c r="U128">
         <v>0.32005</v>
       </c>
-      <c r="V128" s="7">
+      <c r="V128">
         <v>370</v>
       </c>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>154</v>
       </c>
@@ -22076,11 +22060,11 @@
       <c r="U129">
         <v>0.40434999999999999</v>
       </c>
-      <c r="V129" s="7">
+      <c r="V129">
         <v>670</v>
       </c>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>155</v>
       </c>
@@ -22144,11 +22128,11 @@
       <c r="U130">
         <v>0.36</v>
       </c>
-      <c r="V130" s="7">
+      <c r="V130">
         <v>520</v>
       </c>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>156</v>
       </c>
@@ -22212,11 +22196,11 @@
       <c r="U131">
         <v>0.34279999999999999</v>
       </c>
-      <c r="V131" s="7">
+      <c r="V131">
         <v>280</v>
       </c>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -22280,11 +22264,11 @@
       <c r="U132">
         <v>0.32815</v>
       </c>
-      <c r="V132" s="7">
+      <c r="V132">
         <v>310</v>
       </c>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -22348,11 +22332,11 @@
       <c r="U133">
         <v>0.33115</v>
       </c>
-      <c r="V133" s="7">
+      <c r="V133">
         <v>490</v>
       </c>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>159</v>
       </c>
@@ -22416,11 +22400,11 @@
       <c r="U134">
         <v>0.38834999999999997</v>
       </c>
-      <c r="V134" s="7">
+      <c r="V134">
         <v>970</v>
       </c>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>160</v>
       </c>
@@ -22484,11 +22468,11 @@
       <c r="U135">
         <v>0.25445000000000001</v>
       </c>
-      <c r="V135" s="7">
+      <c r="V135">
         <v>2080</v>
       </c>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>161</v>
       </c>
@@ -22552,11 +22536,11 @@
       <c r="U136">
         <v>0.1883</v>
       </c>
-      <c r="V136" s="7">
+      <c r="V136">
         <v>240</v>
       </c>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>162</v>
       </c>
@@ -22620,11 +22604,11 @@
       <c r="U137">
         <v>0.40244999999999997</v>
       </c>
-      <c r="V137" s="7">
+      <c r="V137">
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>163</v>
       </c>
@@ -22688,11 +22672,11 @@
       <c r="U138">
         <v>0.37714999999999999</v>
       </c>
-      <c r="V138" s="7">
+      <c r="V138">
         <v>790</v>
       </c>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>164</v>
       </c>
@@ -22756,11 +22740,11 @@
       <c r="U139">
         <v>0.27915000000000001</v>
       </c>
-      <c r="V139" s="7">
+      <c r="V139">
         <v>340</v>
       </c>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>165</v>
       </c>
@@ -22824,11 +22808,11 @@
       <c r="U140">
         <v>0.17710000000000001</v>
       </c>
-      <c r="V140" s="7">
+      <c r="V140">
         <v>680</v>
       </c>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>166</v>
       </c>
@@ -22892,11 +22876,11 @@
       <c r="U141">
         <v>0.18625</v>
       </c>
-      <c r="V141" s="7">
+      <c r="V141">
         <v>570</v>
       </c>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>167</v>
       </c>
@@ -22960,11 +22944,11 @@
       <c r="U142">
         <v>0.17915</v>
       </c>
-      <c r="V142" s="7">
+      <c r="V142">
         <v>550</v>
       </c>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>168</v>
       </c>
@@ -23028,11 +23012,11 @@
       <c r="U143">
         <v>0.16450000000000001</v>
       </c>
-      <c r="V143" s="7">
+      <c r="V143">
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>169</v>
       </c>
@@ -23096,11 +23080,11 @@
       <c r="U144">
         <v>0.16335</v>
       </c>
-      <c r="V144" s="7">
+      <c r="V144">
         <v>90</v>
       </c>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>170</v>
       </c>
@@ -23164,11 +23148,11 @@
       <c r="U145">
         <v>0.38834999999999997</v>
       </c>
-      <c r="V145" s="7">
+      <c r="V145">
         <v>800</v>
       </c>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>171</v>
       </c>
@@ -23232,11 +23216,11 @@
       <c r="U146">
         <v>0.34515000000000001</v>
       </c>
-      <c r="V146" s="7">
+      <c r="V146">
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>172</v>
       </c>
@@ -23300,11 +23284,11 @@
       <c r="U147">
         <v>0.34110000000000001</v>
       </c>
-      <c r="V147" s="7">
+      <c r="V147">
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>173</v>
       </c>
@@ -23368,11 +23352,11 @@
       <c r="U148">
         <v>0.37790000000000001</v>
       </c>
-      <c r="V148" s="7">
+      <c r="V148">
         <v>110</v>
       </c>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>174</v>
       </c>
@@ -23436,11 +23420,11 @@
       <c r="U149">
         <v>0.36354999999999998</v>
       </c>
-      <c r="V149" s="7">
+      <c r="V149">
         <v>60</v>
       </c>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>175</v>
       </c>
@@ -23504,323 +23488,8 @@
       <c r="U150">
         <v>0.17155000000000001</v>
       </c>
-      <c r="V150" s="7">
+      <c r="V150">
         <v>410</v>
-      </c>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A151" t="s">
-        <v>176</v>
-      </c>
-      <c r="B151">
-        <v>3.0790000000000002</v>
-      </c>
-      <c r="C151">
-        <v>13.257999999999999</v>
-      </c>
-      <c r="D151">
-        <v>0.41499999999999998</v>
-      </c>
-      <c r="E151">
-        <v>8.9909999999999997</v>
-      </c>
-      <c r="F151">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="G151">
-        <v>3.964</v>
-      </c>
-      <c r="H151">
-        <v>51.106999999999999</v>
-      </c>
-      <c r="I151">
-        <v>5.31</v>
-      </c>
-      <c r="J151">
-        <v>12.804</v>
-      </c>
-      <c r="K151">
-        <v>0.16300000000000001</v>
-      </c>
-      <c r="L151"/>
-      <c r="M151">
-        <v>0</v>
-      </c>
-      <c r="N151">
-        <v>0.2448962650152364</v>
-      </c>
-      <c r="O151">
-        <v>37.453400000000002</v>
-      </c>
-      <c r="P151">
-        <v>38.354900000000001</v>
-      </c>
-      <c r="Q151">
-        <v>24.145499999999998</v>
-      </c>
-      <c r="R151">
-        <v>2.5100000000000001E-2</v>
-      </c>
-      <c r="S151">
-        <v>0.22745000000000001</v>
-      </c>
-      <c r="T151">
-        <v>0.30680000000000002</v>
-      </c>
-      <c r="U151">
-        <v>0.17699999999999999</v>
-      </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A152" t="s">
-        <v>177</v>
-      </c>
-      <c r="B152">
-        <v>2.04</v>
-      </c>
-      <c r="C152">
-        <v>11.221</v>
-      </c>
-      <c r="D152">
-        <v>0.45400000000000001</v>
-      </c>
-      <c r="E152">
-        <v>9.8230000000000004</v>
-      </c>
-      <c r="F152">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="G152">
-        <v>2.09</v>
-      </c>
-      <c r="H152">
-        <v>49.228000000000002</v>
-      </c>
-      <c r="I152">
-        <v>13.143000000000001</v>
-      </c>
-      <c r="J152">
-        <v>11.334</v>
-      </c>
-      <c r="K152">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="L152"/>
-      <c r="M152">
-        <v>0</v>
-      </c>
-      <c r="N152">
-        <v>0.10984559417596036</v>
-      </c>
-      <c r="O152">
-        <v>47.4559</v>
-      </c>
-      <c r="P152">
-        <v>40.443199999999997</v>
-      </c>
-      <c r="Q152">
-        <v>11.046849999999999</v>
-      </c>
-      <c r="R152">
-        <v>5.2650000000000002E-2</v>
-      </c>
-      <c r="S152">
-        <v>0.23685</v>
-      </c>
-      <c r="T152">
-        <v>0.14445</v>
-      </c>
-      <c r="U152">
-        <v>0.39755000000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A153" t="s">
-        <v>178</v>
-      </c>
-      <c r="B153">
-        <v>2.21</v>
-      </c>
-      <c r="C153">
-        <v>12.298</v>
-      </c>
-      <c r="D153">
-        <v>0.26800000000000002</v>
-      </c>
-      <c r="E153">
-        <v>11.002000000000001</v>
-      </c>
-      <c r="F153">
-        <v>0.48899999999999999</v>
-      </c>
-      <c r="G153">
-        <v>2.649</v>
-      </c>
-      <c r="H153">
-        <v>49.515999999999998</v>
-      </c>
-      <c r="I153">
-        <v>9.81</v>
-      </c>
-      <c r="J153">
-        <v>11.347</v>
-      </c>
-      <c r="K153">
-        <v>0.23200000000000001</v>
-      </c>
-      <c r="L153"/>
-      <c r="M153">
-        <v>0</v>
-      </c>
-      <c r="N153">
-        <v>0.18780555925155926</v>
-      </c>
-      <c r="O153">
-        <v>44.957250000000002</v>
-      </c>
-      <c r="P153">
-        <v>39.902200000000001</v>
-      </c>
-      <c r="Q153">
-        <v>14.00465</v>
-      </c>
-      <c r="R153">
-        <v>4.3200000000000002E-2</v>
-      </c>
-      <c r="S153">
-        <v>0.25314999999999999</v>
-      </c>
-      <c r="T153">
-        <v>0.18465000000000001</v>
-      </c>
-      <c r="U153">
-        <v>0.34905000000000003</v>
-      </c>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A154" t="s">
-        <v>179</v>
-      </c>
-      <c r="B154">
-        <v>2.3889999999999998</v>
-      </c>
-      <c r="C154">
-        <v>11.837999999999999</v>
-      </c>
-      <c r="D154">
-        <v>0.21</v>
-      </c>
-      <c r="E154">
-        <v>10.051</v>
-      </c>
-      <c r="F154">
-        <v>0.375</v>
-      </c>
-      <c r="G154">
-        <v>2.032</v>
-      </c>
-      <c r="H154">
-        <v>50.027000000000001</v>
-      </c>
-      <c r="I154">
-        <v>11.39</v>
-      </c>
-      <c r="J154">
-        <v>11.336</v>
-      </c>
-      <c r="K154">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="L154"/>
-      <c r="M154">
-        <v>0</v>
-      </c>
-      <c r="N154">
-        <v>0.14908791720483525</v>
-      </c>
-      <c r="O154">
-        <v>46.474899999999998</v>
-      </c>
-      <c r="P154">
-        <v>40.2682</v>
-      </c>
-      <c r="Q154">
-        <v>12.497450000000001</v>
-      </c>
-      <c r="R154">
-        <v>5.0200000000000002E-2</v>
-      </c>
-      <c r="S154">
-        <v>0.22225</v>
-      </c>
-      <c r="T154">
-        <v>0.16239999999999999</v>
-      </c>
-      <c r="U154">
-        <v>0.36599999999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="A155" t="s">
-        <v>180</v>
-      </c>
-      <c r="B155">
-        <v>2.089</v>
-      </c>
-      <c r="C155">
-        <v>11.045999999999999</v>
-      </c>
-      <c r="D155">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="E155">
-        <v>9.3949999999999996</v>
-      </c>
-      <c r="F155">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="G155">
-        <v>1.869</v>
-      </c>
-      <c r="H155">
-        <v>49.73</v>
-      </c>
-      <c r="I155">
-        <v>13.7</v>
-      </c>
-      <c r="J155">
-        <v>11.336</v>
-      </c>
-      <c r="K155">
-        <v>0.13500000000000001</v>
-      </c>
-      <c r="L155"/>
-      <c r="M155">
-        <v>0</v>
-      </c>
-      <c r="N155">
-        <v>0.10878728471899675</v>
-      </c>
-      <c r="O155">
-        <v>47.512500000000003</v>
-      </c>
-      <c r="P155">
-        <v>40.510300000000001</v>
-      </c>
-      <c r="Q155">
-        <v>10.67135</v>
-      </c>
-      <c r="R155">
-        <v>4.9250000000000002E-2</v>
-      </c>
-      <c r="S155">
-        <v>0.22605</v>
-      </c>
-      <c r="T155">
-        <v>0.13469999999999999</v>
-      </c>
-      <c r="U155">
-        <v>0.38390000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -23831,11 +23500,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA87C337-5F2D-7949-BD40-54BCEC094090}">
   <dimension ref="A1:Y45"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -23868,51 +23537,51 @@
         <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N1" t="s">
         <v>24</v>
       </c>
       <c r="O1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="P1" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="Q1" t="s">
+        <v>342</v>
+      </c>
+      <c r="R1" t="s">
+        <v>343</v>
+      </c>
+      <c r="S1" t="s">
+        <v>344</v>
+      </c>
+      <c r="T1" t="s">
+        <v>345</v>
+      </c>
+      <c r="U1" t="s">
+        <v>346</v>
+      </c>
+      <c r="V1" t="s">
         <v>347</v>
       </c>
-      <c r="R1" t="s">
+      <c r="W1" t="s">
         <v>348</v>
       </c>
-      <c r="S1" t="s">
+      <c r="X1" t="s">
         <v>349</v>
       </c>
-      <c r="T1" t="s">
+      <c r="Y1" t="s">
         <v>350</v>
       </c>
-      <c r="U1" t="s">
-        <v>351</v>
-      </c>
-      <c r="V1" t="s">
-        <v>352</v>
-      </c>
-      <c r="W1" t="s">
-        <v>353</v>
-      </c>
-      <c r="X1" t="s">
-        <v>354</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B2">
         <v>2.5575994910094542</v>
@@ -23987,9 +23656,9 @@
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B3">
         <v>3.0211247806699704</v>
@@ -24064,9 +23733,9 @@
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B4">
         <v>2.5103717887832802</v>
@@ -24141,9 +23810,9 @@
         <v>0.24865000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B5">
         <v>2.7166278089205695</v>
@@ -24212,9 +23881,9 @@
         <v>0.31945000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B6">
         <v>2.4079811252236323</v>
@@ -24289,9 +23958,9 @@
         <v>0.26960000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B7">
         <v>2.9197646859199344</v>
@@ -24366,9 +24035,9 @@
         <v>0.31945000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B8">
         <v>2.4231005369746721</v>
@@ -24443,9 +24112,9 @@
         <v>0.33029999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B9">
         <v>2.4859169276815742</v>
@@ -24520,9 +24189,9 @@
         <v>0.33800000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B10">
         <v>2.5396542961624085</v>
@@ -24597,9 +24266,9 @@
         <v>0.37580000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B11">
         <v>2.8934270818082752</v>
@@ -24674,9 +24343,9 @@
         <v>0.69930000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B12">
         <v>2.7220000758910428</v>
@@ -24751,9 +24420,9 @@
         <v>0.70065</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B13">
         <v>2.5288395609629921</v>
@@ -24822,9 +24491,9 @@
         <v>0.38390000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B14">
         <v>3.3345335364451243</v>
@@ -24899,9 +24568,9 @@
         <v>6.1199999999999997E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B15">
         <v>2.8361103162476642</v>
@@ -24976,9 +24645,9 @@
         <v>4.0750000000000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B16">
         <v>2.9528928982514793</v>
@@ -25053,9 +24722,9 @@
         <v>0.27024999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B17">
         <v>2.6036245889206291</v>
@@ -25130,9 +24799,9 @@
         <v>0.14779999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B18">
         <v>2.9956540144096664</v>
@@ -25207,9 +24876,9 @@
         <v>0.51390000000000002</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B19">
         <v>2.8702388275757706</v>
@@ -25284,9 +24953,9 @@
         <v>0.32755000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B20">
         <v>2.9800655214147316</v>
@@ -25361,9 +25030,9 @@
         <v>0.13320000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B21">
         <v>1.1493192238269572</v>
@@ -25438,9 +25107,9 @@
         <v>8.14E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B22">
         <v>2.7691902741354015</v>
@@ -25515,9 +25184,9 @@
         <v>6.4750000000000002E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B23">
         <v>2.8831241162400127</v>
@@ -25592,9 +25261,9 @@
         <v>0.31724999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B24">
         <v>2.3294476830173281</v>
@@ -25669,9 +25338,9 @@
         <v>0.2117</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B25">
         <v>2.4784407500755976</v>
@@ -25746,9 +25415,9 @@
         <v>0.50149999999999995</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B26">
         <v>3.3699543487576422</v>
@@ -25823,9 +25492,9 @@
         <v>0.29335</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B27">
         <v>3.0841410046278113</v>
@@ -25900,9 +25569,9 @@
         <v>0.24310000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B28">
         <v>2.7746763886768151</v>
@@ -25977,9 +25646,9 @@
         <v>0.1588</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B29">
         <v>3.0701521146223349</v>
@@ -26054,9 +25723,9 @@
         <v>0.17765</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B30">
         <v>2.5210711301392008</v>
@@ -26131,9 +25800,9 @@
         <v>0.15434999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B31">
         <v>1.7454146599663414</v>
@@ -26208,9 +25877,9 @@
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B32">
         <v>2.9341272559973195</v>
@@ -26285,9 +25954,9 @@
         <v>7.6E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B33">
         <v>2.8892370183117642</v>
@@ -26362,9 +26031,9 @@
         <v>1.7350000000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="B34">
         <v>3.0905362984579066</v>
@@ -26439,9 +26108,9 @@
         <v>0.47189999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B35">
         <v>3.1708582609001406</v>
@@ -26516,9 +26185,9 @@
         <v>0.18290000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B36">
         <v>2.8627573250379665</v>
@@ -26593,9 +26262,9 @@
         <v>0.38140000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B37">
         <v>3.0575975486130971</v>
@@ -26670,9 +26339,9 @@
         <v>0.26850000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B38">
         <v>2.8553107598379115</v>
@@ -26747,9 +26416,9 @@
         <v>0.29604999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B39">
         <v>2.8931454891309891</v>
@@ -26824,9 +26493,9 @@
         <v>0.32114999999999999</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B40">
         <v>3.081665517532802</v>
@@ -26901,9 +26570,9 @@
         <v>0.26300000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B41">
         <v>2.7998689234913705</v>
@@ -26978,9 +26647,9 @@
         <v>0.22855</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B42">
         <v>2.9634662632059512</v>
@@ -27055,9 +26724,9 @@
         <v>0.28355000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B43">
         <v>2.8689112792544327</v>
@@ -27132,9 +26801,9 @@
         <v>0.33894999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B44">
         <v>2.9494104744341976</v>
@@ -27203,9 +26872,9 @@
         <v>0.2752</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B45">
         <v>2.7721624590964815</v>
@@ -27282,14 +26951,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA4ADEE-1D75-BA4F-9D07-A934D74DA0AC}">
   <dimension ref="A1:X102"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.58203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
@@ -27322,48 +26991,48 @@
         <v>23</v>
       </c>
       <c r="L1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="M1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="N1" t="s">
         <v>24</v>
       </c>
       <c r="O1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="P1" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>334</v>
+      </c>
+      <c r="R1" t="s">
+        <v>335</v>
+      </c>
+      <c r="S1" t="s">
+        <v>336</v>
+      </c>
+      <c r="T1" t="s">
+        <v>337</v>
+      </c>
+      <c r="U1" t="s">
         <v>338</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="V1" t="s">
         <v>339</v>
       </c>
-      <c r="R1" t="s">
+      <c r="W1" t="s">
         <v>340</v>
       </c>
-      <c r="S1" t="s">
+      <c r="X1" t="s">
         <v>341</v>
       </c>
-      <c r="T1" t="s">
-        <v>342</v>
-      </c>
-      <c r="U1" t="s">
-        <v>343</v>
-      </c>
-      <c r="V1" t="s">
-        <v>344</v>
-      </c>
-      <c r="W1" t="s">
-        <v>345</v>
-      </c>
-      <c r="X1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B2">
         <v>5.7967000000000004</v>
@@ -27405,7 +27074,7 @@
         <v>4.6343336799999996E-2</v>
       </c>
       <c r="O2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P2">
         <v>5.8163999999999998</v>
@@ -27435,9 +27104,9 @@
         <v>7.3000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B3">
         <v>2.6326000000000001</v>
@@ -27479,7 +27148,7 @@
         <v>0.32180092399999999</v>
       </c>
       <c r="O3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P3">
         <v>4.0690999999999997</v>
@@ -27509,9 +27178,9 @@
         <v>9.1500000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B4">
         <v>3.0295999999999998</v>
@@ -27553,7 +27222,7 @@
         <v>0.29927986400000001</v>
       </c>
       <c r="O4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P4">
         <v>3.9868000000000001</v>
@@ -27583,9 +27252,9 @@
         <v>1.925E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B5">
         <v>2.6976</v>
@@ -27627,7 +27296,7 @@
         <v>0.3445221712</v>
       </c>
       <c r="O5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="P5">
         <v>4.1756000000000002</v>
@@ -27657,9 +27326,9 @@
         <v>3.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B6">
         <v>2.9977999999999998</v>
@@ -27701,7 +27370,7 @@
         <v>0.37114706879999998</v>
       </c>
       <c r="O6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="P6">
         <v>4.4211</v>
@@ -27731,9 +27400,9 @@
         <v>1.65E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B7">
         <v>2.9977999999999998</v>
@@ -27775,7 +27444,7 @@
         <v>0.37114706879999998</v>
       </c>
       <c r="O7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P7">
         <v>4.4516499999999999</v>
@@ -27805,9 +27474,9 @@
         <v>2.1950000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B8">
         <v>2.7690000000000001</v>
@@ -27849,7 +27518,7 @@
         <v>0.25964279839999999</v>
       </c>
       <c r="O8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="P8">
         <v>5.8003999999999998</v>
@@ -27879,9 +27548,9 @@
         <v>-3.8949999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B9">
         <v>2.8681999999999999</v>
@@ -27917,7 +27586,7 @@
         <v>0.33441271760000002</v>
       </c>
       <c r="O9" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="P9">
         <v>5.2889499999999998</v>
@@ -27947,9 +27616,9 @@
         <v>2.5350000000000001E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B10">
         <v>3.3010000000000002</v>
@@ -27985,7 +27654,7 @@
         <v>0.3817569904</v>
       </c>
       <c r="O10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="P10">
         <v>3.65835</v>
@@ -28015,9 +27684,9 @@
         <v>-8.9499999999999996E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B11">
         <v>2.9971000000000001</v>
@@ -28059,7 +27728,7 @@
         <v>0.34772516640000001</v>
       </c>
       <c r="O11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="P11">
         <v>4.3895</v>
@@ -28089,9 +27758,9 @@
         <v>-6.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B12">
         <v>2.6231</v>
@@ -28133,7 +27802,7 @@
         <v>0.21660255040000001</v>
       </c>
       <c r="O12" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="P12">
         <v>5.6790500000000002</v>
@@ -28163,9 +27832,9 @@
         <v>-1.4449999999999999E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B13">
         <v>3.0588000000000002</v>
@@ -28207,7 +27876,7 @@
         <v>0.37264847279999996</v>
       </c>
       <c r="O13" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P13">
         <v>4.4504999999999999</v>
@@ -28237,9 +27906,9 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B14">
         <v>2.8955000000000002</v>
@@ -28281,7 +27950,7 @@
         <v>0.33341178160000001</v>
       </c>
       <c r="O14" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="P14">
         <v>3.8226499999999999</v>
@@ -28311,9 +27980,9 @@
         <v>3.3099999999999997E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B15">
         <v>4.3959000000000001</v>
@@ -28355,7 +28024,7 @@
         <v>3.8836316799999999E-2</v>
       </c>
       <c r="O15" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="P15">
         <v>6.1832000000000003</v>
@@ -28385,9 +28054,9 @@
         <v>-1.0749999999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B16">
         <v>4.1863000000000001</v>
@@ -28429,7 +28098,7 @@
         <v>7.4469638399999996E-2</v>
       </c>
       <c r="O16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="P16">
         <v>6.2660999999999998</v>
@@ -28459,9 +28128,9 @@
         <v>-3.2899999999999999E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B17">
         <v>3.7968000000000002</v>
@@ -28503,7 +28172,7 @@
         <v>0.106599684</v>
       </c>
       <c r="O17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P17">
         <v>5.8825500000000002</v>
@@ -28533,9 +28202,9 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B18">
         <v>4.1958000000000002</v>
@@ -28577,7 +28246,7 @@
         <v>0.13202345840000002</v>
       </c>
       <c r="O18" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="P18">
         <v>5.4261499999999998</v>
@@ -28607,9 +28276,9 @@
         <v>5.2299999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B19">
         <v>2.9746999999999999</v>
@@ -28651,7 +28320,7 @@
         <v>0.11410670399999999</v>
       </c>
       <c r="O19" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="P19">
         <v>5.9219999999999997</v>
@@ -28681,9 +28350,9 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B20">
         <v>4.0308000000000002</v>
@@ -28725,7 +28394,7 @@
         <v>0.11230501919999999</v>
       </c>
       <c r="O20" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P20">
         <v>6.8426999999999998</v>
@@ -28755,9 +28424,9 @@
         <v>-5.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B21">
         <v>5.1257000000000001</v>
@@ -28799,7 +28468,7 @@
         <v>7.5270387200000011E-2</v>
       </c>
       <c r="O21" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="P21">
         <v>5.9173999999999998</v>
@@ -28829,9 +28498,9 @@
         <v>9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B22">
         <v>5.0956999999999999</v>
@@ -28873,7 +28542,7 @@
         <v>5.0847548799999996E-2</v>
       </c>
       <c r="O22" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P22">
         <v>5.9923500000000001</v>
@@ -28903,9 +28572,9 @@
         <v>1.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B23">
         <v>4.4497</v>
@@ -28941,7 +28610,7 @@
         <v>1.92179712E-2</v>
       </c>
       <c r="O23" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="P23">
         <v>5.8979999999999997</v>
@@ -28971,9 +28640,9 @@
         <v>7.8499999999999993E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B24">
         <v>3.927</v>
@@ -29015,7 +28684,7 @@
         <v>5.9855972799999997E-2</v>
       </c>
       <c r="O24" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="P24">
         <v>6.2759499999999999</v>
@@ -29045,9 +28714,9 @@
         <v>3.5749999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B25">
         <v>4.9062000000000001</v>
@@ -29089,7 +28758,7 @@
         <v>6.6562243999999993E-2</v>
       </c>
       <c r="O25" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P25">
         <v>6.5931499999999996</v>
@@ -29119,9 +28788,9 @@
         <v>2.12E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B26">
         <v>2.3761000000000001</v>
@@ -29163,7 +28832,7 @@
         <v>0.21700292479999997</v>
       </c>
       <c r="O26" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="P26">
         <v>2.9722499999999998</v>
@@ -29193,9 +28862,9 @@
         <v>1.635E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B27">
         <v>4.2130999999999998</v>
@@ -29237,7 +28906,7 @@
         <v>7.8173101599999989E-2</v>
       </c>
       <c r="O27" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P27">
         <v>5.8152999999999997</v>
@@ -29267,9 +28936,9 @@
         <v>6.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B28">
         <v>4.2774000000000001</v>
@@ -29305,7 +28974,7 @@
         <v>8.0675441599999995E-2</v>
       </c>
       <c r="O28" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="P28">
         <v>5.8983499999999998</v>
@@ -29335,9 +29004,9 @@
         <v>-5.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B29">
         <v>4.1772</v>
@@ -29379,7 +29048,7 @@
         <v>0.12691868480000001</v>
       </c>
       <c r="O29" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="P29">
         <v>5.5066499999999996</v>
@@ -29409,9 +29078,9 @@
         <v>-1.315E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B30">
         <v>2.6684000000000001</v>
@@ -29453,7 +29122,7 @@
         <v>0.17296174080000001</v>
       </c>
       <c r="O30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P30">
         <v>4.4394499999999999</v>
@@ -29483,9 +29152,9 @@
         <v>1.4500000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B31">
         <v>2.4885000000000002</v>
@@ -29527,7 +29196,7 @@
         <v>0.33711524479999999</v>
       </c>
       <c r="O31" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="P31">
         <v>3.48</v>
@@ -29557,9 +29226,9 @@
         <v>1.43E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B32">
         <v>2.2776999999999998</v>
@@ -29601,7 +29270,7 @@
         <v>0.30788791360000001</v>
       </c>
       <c r="O32" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P32">
         <v>3.9377499999999999</v>
@@ -29631,9 +29300,9 @@
         <v>3.2349999999999997E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B33">
         <v>3.1248</v>
@@ -29675,7 +29344,7 @@
         <v>0.33521346639999999</v>
       </c>
       <c r="O33" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P33">
         <v>3.7087500000000002</v>
@@ -29705,9 +29374,9 @@
         <v>-2.3199999999999998E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B34">
         <v>3.1206999999999998</v>
@@ -29749,7 +29418,7 @@
         <v>0.34692441760000003</v>
       </c>
       <c r="O34" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="P34">
         <v>3.7087500000000002</v>
@@ -29779,9 +29448,9 @@
         <v>-2.3199999999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B35">
         <v>2.8180999999999998</v>
@@ -29823,7 +29492,7 @@
         <v>0.32970831840000003</v>
       </c>
       <c r="O35" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P35">
         <v>4.2669499999999996</v>
@@ -29853,9 +29522,9 @@
         <v>-3.4450000000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B36">
         <v>3.0550999999999999</v>
@@ -29897,7 +29566,7 @@
         <v>0.30408435679999996</v>
       </c>
       <c r="O36" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P36">
         <v>4.3008499999999996</v>
@@ -29927,9 +29596,9 @@
         <v>9.7000000000000003E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B37">
         <v>3.0804</v>
@@ -29971,7 +29640,7 @@
         <v>0.33951749120000002</v>
       </c>
       <c r="O37" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="P37">
         <v>4.03735</v>
@@ -30001,9 +29670,9 @@
         <v>-7.6499999999999997E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B38">
         <v>3.5804</v>
@@ -30045,7 +29714,7 @@
         <v>0.1744631448</v>
       </c>
       <c r="O38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="P38">
         <v>4.9722499999999998</v>
@@ -30075,9 +29744,9 @@
         <v>-8.6E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B39">
         <v>4.0648999999999997</v>
@@ -30119,7 +29788,7 @@
         <v>0.174663332</v>
       </c>
       <c r="O39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="P39">
         <v>5.3695000000000004</v>
@@ -30149,9 +29818,9 @@
         <v>1.5650000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B40">
         <v>4.6753999999999998</v>
@@ -30193,7 +29862,7 @@
         <v>0.11460717199999999</v>
       </c>
       <c r="O40" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P40">
         <v>5.6173500000000001</v>
@@ -30223,9 +29892,9 @@
         <v>2.41E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B41">
         <v>4.8288000000000002</v>
@@ -30267,7 +29936,7 @@
         <v>6.8964490399999995E-2</v>
       </c>
       <c r="O41" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="P41">
         <v>5.8012499999999996</v>
@@ -30297,9 +29966,9 @@
         <v>6.0499999999999998E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B42">
         <v>4.7805999999999997</v>
@@ -30341,7 +30010,7 @@
         <v>6.67624312E-2</v>
       </c>
       <c r="O42" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="P42">
         <v>5.8257500000000002</v>
@@ -30371,9 +30040,9 @@
         <v>1.255E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B43">
         <v>4.8131000000000004</v>
@@ -30415,7 +30084,7 @@
         <v>9.829191520000001E-2</v>
       </c>
       <c r="O43" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P43">
         <v>5.5018500000000001</v>
@@ -30445,9 +30114,9 @@
         <v>2.0500000000000002E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B44">
         <v>5.0624000000000002</v>
@@ -30489,7 +30158,7 @@
         <v>4.5142213600000002E-2</v>
       </c>
       <c r="O44" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="P44">
         <v>6.0791000000000004</v>
@@ -30519,9 +30188,9 @@
         <v>3.175E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B45">
         <v>4.5015999999999998</v>
@@ -30563,7 +30232,7 @@
         <v>5.8054287999999996E-2</v>
       </c>
       <c r="O45" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P45">
         <v>6.1228999999999996</v>
@@ -30593,9 +30262,9 @@
         <v>-1.8100000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B46">
         <v>5.1999000000000004</v>
@@ -30637,7 +30306,7 @@
         <v>4.29401544E-2</v>
       </c>
       <c r="O46" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="P46">
         <v>6.0083000000000002</v>
@@ -30667,9 +30336,9 @@
         <v>-4.45E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B47">
         <v>3.5434000000000001</v>
@@ -30711,7 +30380,7 @@
         <v>0.12051269440000001</v>
       </c>
       <c r="O47" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P47">
         <v>5.3223000000000003</v>
@@ -30741,9 +30410,9 @@
         <v>-1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B48">
         <v>2.7900999999999998</v>
@@ -30785,7 +30454,7 @@
         <v>0.30998987919999998</v>
       </c>
       <c r="O48" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="P48">
         <v>4.3325500000000003</v>
@@ -30815,9 +30484,9 @@
         <v>-6.4999999999999997E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B49">
         <v>2.221428998526044</v>
@@ -30859,7 +30528,7 @@
         <v>0.16036590245133395</v>
       </c>
       <c r="O49" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="P49">
         <v>2.7955999999999999</v>
@@ -30889,9 +30558,9 @@
         <v>1.9550000000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B50">
         <v>2.1486812211602855</v>
@@ -30933,7 +30602,7 @@
         <v>0.16366000300689346</v>
       </c>
       <c r="O50" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="P50">
         <v>3.1286999999999998</v>
@@ -30963,9 +30632,9 @@
         <v>-2.3650000000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B51">
         <v>2.3660780846592613</v>
@@ -31007,7 +30676,7 @@
         <v>0.14244529986135757</v>
       </c>
       <c r="O51" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="P51">
         <v>3.0670999999999999</v>
@@ -31037,9 +30706,9 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B52">
         <v>4.3818999999999999</v>
@@ -31081,7 +30750,7 @@
         <v>9.6189949600000005E-2</v>
       </c>
       <c r="O52" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P52">
         <v>5.6254999999999997</v>
@@ -31111,9 +30780,9 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B53">
         <v>4.8010000000000002</v>
@@ -31155,7 +30824,7 @@
         <v>5.3750263199999995E-2</v>
       </c>
       <c r="O53" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P53">
         <v>6.1519000000000004</v>
@@ -31185,9 +30854,9 @@
         <v>1.1599999999999999E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B54">
         <v>4.7005999999999997</v>
@@ -31229,7 +30898,7 @@
         <v>5.3550076000000002E-2</v>
       </c>
       <c r="O54" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="P54">
         <v>5.9764499999999998</v>
@@ -31259,9 +30928,9 @@
         <v>-3.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B55">
         <v>4.6740000000000004</v>
@@ -31303,7 +30972,7 @@
         <v>5.1648297600000004E-2</v>
       </c>
       <c r="O55" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P55">
         <v>6.0884999999999998</v>
@@ -31333,9 +31002,9 @@
         <v>2.4649999999999998E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B56">
         <v>3.9289999999999998</v>
@@ -31377,7 +31046,7 @@
         <v>5.0847548799999996E-2</v>
       </c>
       <c r="O56" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P56">
         <v>5.8790500000000003</v>
@@ -31407,9 +31076,9 @@
         <v>-6.5500000000000003E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B57">
         <v>4.9714</v>
@@ -31451,7 +31120,7 @@
         <v>5.5051480000000007E-2</v>
       </c>
       <c r="O57" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P57">
         <v>6.2962999999999996</v>
@@ -31481,9 +31150,9 @@
         <v>1.3350000000000001E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B58">
         <v>4.2245999999999997</v>
@@ -31525,7 +31194,7 @@
         <v>8.7281619199999994E-2</v>
       </c>
       <c r="O58" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P58">
         <v>5.9504999999999999</v>
@@ -31555,9 +31224,9 @@
         <v>-2.7050000000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B59">
         <v>4.2054999999999998</v>
@@ -31599,7 +31268,7 @@
         <v>0.17856698240000002</v>
       </c>
       <c r="O59" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P59">
         <v>5.5073999999999996</v>
@@ -31629,9 +31298,9 @@
         <v>9.1000000000000004E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B60">
         <v>3.4577</v>
@@ -31673,7 +31342,7 @@
         <v>0.134625892</v>
       </c>
       <c r="O60" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P60">
         <v>5.3223000000000003</v>
@@ -31703,9 +31372,9 @@
         <v>-1.9900000000000001E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B61">
         <v>4.6836000000000002</v>
@@ -31747,7 +31416,7 @@
         <v>5.5852228800000001E-2</v>
       </c>
       <c r="O61" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P61">
         <v>5.7946999999999997</v>
@@ -31777,9 +31446,9 @@
         <v>-1.95E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -31821,7 +31490,7 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P62">
         <v>6.3872499999999999</v>
@@ -31851,9 +31520,9 @@
         <v>1.3050000000000001E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B63">
         <v>4.7926000000000002</v>
@@ -31895,7 +31564,7 @@
         <v>0.11240511280000001</v>
       </c>
       <c r="O63" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="P63">
         <v>5.1853999999999996</v>
@@ -31925,9 +31594,9 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B64">
         <v>5.5945</v>
@@ -31969,7 +31638,7 @@
         <v>3.3030888000000001E-2</v>
       </c>
       <c r="O64" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="P64">
         <v>6.8752500000000003</v>
@@ -31999,9 +31668,9 @@
         <v>2.7550000000000002E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B65">
         <v>2.9508000000000001</v>
@@ -32043,7 +31712,7 @@
         <v>0.21550152079999998</v>
       </c>
       <c r="O65" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="P65">
         <v>4.3014999999999999</v>
@@ -32073,9 +31742,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B66">
         <v>3.0644</v>
@@ -32117,7 +31786,7 @@
         <v>0.294775652</v>
       </c>
       <c r="O66" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="P66">
         <v>4.3014999999999999</v>
@@ -32147,9 +31816,9 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B67">
         <v>2.8435999999999999</v>
@@ -32191,7 +31860,7 @@
         <v>0.31809746080000001</v>
       </c>
       <c r="O67" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P67">
         <v>4.3390000000000004</v>
@@ -32221,9 +31890,9 @@
         <v>-1.11E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B68">
         <v>2.9569999999999999</v>
@@ -32265,7 +31934,7 @@
         <v>0.3119917512</v>
       </c>
       <c r="O68" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="P68">
         <v>4.2060000000000004</v>
@@ -32295,9 +31964,9 @@
         <v>-2.2499999999999998E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B69">
         <v>3.1051000000000002</v>
@@ -32339,7 +32008,7 @@
         <v>0.33130981599999998</v>
       </c>
       <c r="O69" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="P69">
         <v>4.6478999999999999</v>
@@ -32369,9 +32038,9 @@
         <v>-6.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B70">
         <v>2.8228</v>
@@ -32413,7 +32082,7 @@
         <v>0.3209000816</v>
       </c>
       <c r="O70" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="P70">
         <v>4.0366499999999998</v>
@@ -32443,9 +32112,9 @@
         <v>-3.6850000000000001E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B71">
         <v>2.3839135987714895</v>
@@ -32487,7 +32156,7 @@
         <v>0.23177566661548177</v>
       </c>
       <c r="O71" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="P71">
         <v>2.8225500000000001</v>
@@ -32517,9 +32186,9 @@
         <v>-3.2499999999999999E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B72">
         <v>2.4644794100272858</v>
@@ -32561,7 +32230,7 @@
         <v>0.20752926157260554</v>
       </c>
       <c r="O72" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="P72">
         <v>2.6171000000000002</v>
@@ -32591,9 +32260,9 @@
         <v>-5.1500000000000001E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B73">
         <v>3.6172</v>
@@ -32635,7 +32304,7 @@
         <v>9.3387328800000002E-2</v>
       </c>
       <c r="O73" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P73">
         <v>5.8460999999999999</v>
@@ -32665,9 +32334,9 @@
         <v>2.0299999999999999E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B74">
         <v>3.0457000000000001</v>
@@ -32709,7 +32378,7 @@
         <v>0.31999923920000001</v>
       </c>
       <c r="O74" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="P74">
         <v>4.2306999999999997</v>
@@ -32739,9 +32408,9 @@
         <v>3.2000000000000002E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B75">
         <v>3.2311000000000001</v>
@@ -32783,7 +32452,7 @@
         <v>0.32810682080000003</v>
       </c>
       <c r="O75" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="P75">
         <v>4.1543000000000001</v>
@@ -32813,9 +32482,9 @@
         <v>-3.1199999999999999E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B76">
         <v>2.9889999999999999</v>
@@ -32857,7 +32526,7 @@
         <v>0.35002731920000002</v>
       </c>
       <c r="O76" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="P76">
         <v>4.2278000000000002</v>
@@ -32887,9 +32556,9 @@
         <v>-5.57E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B77">
         <v>5.3239999999999998</v>
@@ -32931,7 +32600,7 @@
         <v>6.7463086399999997E-2</v>
       </c>
       <c r="O77" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P77">
         <v>5.5195499999999997</v>
@@ -32961,9 +32630,9 @@
         <v>-3.8999999999999998E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B78">
         <v>2.7953000000000001</v>
@@ -33005,7 +32674,7 @@
         <v>0.33921721040000002</v>
       </c>
       <c r="O78" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="P78">
         <v>3.48685</v>
@@ -33035,9 +32704,9 @@
         <v>3.7249999999999998E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B79">
         <v>3.3744999999999998</v>
@@ -33079,7 +32748,7 @@
         <v>0.24112548240000001</v>
       </c>
       <c r="O79" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="P79">
         <v>4.2020999999999997</v>
@@ -33109,9 +32778,9 @@
         <v>-6.3499999999999997E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B80">
         <v>2.7732999999999999</v>
@@ -33153,7 +32822,7 @@
         <v>0.35593284159999999</v>
       </c>
       <c r="O80" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="P80">
         <v>3.4258500000000001</v>
@@ -33183,9 +32852,9 @@
         <v>-1.43E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B81">
         <v>5.1361999999999997</v>
@@ -33227,7 +32896,7 @@
         <v>0.1056988416</v>
       </c>
       <c r="O81" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="P81">
         <v>5.4939999999999998</v>
@@ -33257,9 +32926,9 @@
         <v>8.8000000000000005E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B82">
         <v>2.7734000000000001</v>
@@ -33301,7 +32970,7 @@
         <v>0.32780653999999998</v>
       </c>
       <c r="O82" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P82">
         <v>2.9815</v>
@@ -33331,9 +33000,9 @@
         <v>1.0149999999999999E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B83">
         <v>2.8146</v>
@@ -33375,7 +33044,7 @@
         <v>0.32480373200000001</v>
       </c>
       <c r="O83" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="P83">
         <v>3.1657500000000001</v>
@@ -33405,9 +33074,9 @@
         <v>1.1950000000000001E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B84">
         <v>2.8614999999999999</v>
@@ -33449,7 +33118,7 @@
         <v>0.33601421519999997</v>
       </c>
       <c r="O84" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="P84">
         <v>3.5467499999999998</v>
@@ -33479,9 +33148,9 @@
         <v>2.085E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B85">
         <v>2.8153000000000001</v>
@@ -33523,7 +33192,7 @@
         <v>0.38716204479999999</v>
       </c>
       <c r="O85" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="P85">
         <v>4.0055500000000004</v>
@@ -33553,9 +33222,9 @@
         <v>1.8599999999999998E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B86">
         <v>3.0411999999999999</v>
@@ -33597,7 +33266,7 @@
         <v>0.35863536880000002</v>
       </c>
       <c r="O86" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="P86">
         <v>3.8585250000000002</v>
@@ -33627,9 +33296,9 @@
         <v>1.065E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B87">
         <v>4.2510000000000003</v>
@@ -33671,7 +33340,7 @@
         <v>0.14423487760000001</v>
       </c>
       <c r="O87" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="P87">
         <v>5.6203000000000003</v>
@@ -33701,9 +33370,9 @@
         <v>7.3000000000000001E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B88">
         <v>4.1992000000000003</v>
@@ -33745,7 +33414,7 @@
         <v>0.10990277280000001</v>
       </c>
       <c r="O88" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="P88">
         <v>5.5980999999999996</v>
@@ -33775,9 +33444,9 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B89">
         <v>4.7199</v>
@@ -33819,7 +33488,7 @@
         <v>4.8245115200000001E-2</v>
       </c>
       <c r="O89" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="P89">
         <v>5.8804499999999997</v>
@@ -33849,9 +33518,9 @@
         <v>-2.7000000000000001E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B90">
         <v>3.3271999999999999</v>
@@ -33887,7 +33556,7 @@
         <v>0.27635842960000001</v>
       </c>
       <c r="O90" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="P90">
         <v>4.0907999999999998</v>
@@ -33917,9 +33586,9 @@
         <v>-3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B91">
         <v>2.8855</v>
@@ -33955,7 +33624,7 @@
         <v>0.35483181199999997</v>
       </c>
       <c r="O91" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P91">
         <v>3.9170500000000001</v>
@@ -33985,9 +33654,9 @@
         <v>-3.9500000000000004E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B92">
         <v>3.0013999999999998</v>
@@ -34023,7 +33692,7 @@
         <v>0.34432198400000003</v>
       </c>
       <c r="O92" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="P92">
         <v>3.7115</v>
@@ -34053,9 +33722,9 @@
         <v>2.7000000000000001E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B93">
         <v>4.0976999999999997</v>
@@ -34091,7 +33760,7 @@
         <v>0.32180092399999999</v>
       </c>
       <c r="O93" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="P93">
         <v>4.3834999999999997</v>
@@ -34121,9 +33790,9 @@
         <v>2.5049999999999999E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B94">
         <v>5.2984999999999998</v>
@@ -34159,7 +33828,7 @@
         <v>6.5761495200000006E-2</v>
       </c>
       <c r="O94" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="P94">
         <v>6.0151000000000003</v>
@@ -34189,9 +33858,9 @@
         <v>2.0400000000000001E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B95">
         <v>2.2672672672280534</v>
@@ -34227,7 +33896,7 @@
         <v>0.16013045717137739</v>
       </c>
       <c r="O95" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="P95">
         <v>2.9971333333333301</v>
@@ -34257,9 +33926,9 @@
         <v>6.9666666666666696E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B96">
         <v>4.0636000000000001</v>
@@ -34295,7 +33964,7 @@
         <v>7.5070200000000004E-2</v>
       </c>
       <c r="O96" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="P96">
         <v>6.1982499999999998</v>
@@ -34325,9 +33994,9 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B97">
         <v>4.399</v>
@@ -34363,7 +34032,7 @@
         <v>9.4188077600000003E-2</v>
       </c>
       <c r="O97" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P97">
         <v>6.2400500000000001</v>
@@ -34393,9 +34062,9 @@
         <v>7.1500000000000001E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B98">
         <v>4.74</v>
@@ -34431,7 +34100,7 @@
         <v>8.4278811199999998E-2</v>
       </c>
       <c r="O98" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="P98">
         <v>5.4822499999999996</v>
@@ -34461,9 +34130,9 @@
         <v>1.5650000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B99">
         <v>3.7951000000000001</v>
@@ -34499,7 +34168,7 @@
         <v>0.1140066104</v>
       </c>
       <c r="O99" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="P99">
         <v>5.2534999999999998</v>
@@ -34529,9 +34198,9 @@
         <v>-7.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B100">
         <v>4.4093999999999998</v>
@@ -34567,7 +34236,7 @@
         <v>7.7172165600000009E-2</v>
       </c>
       <c r="O100" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="P100">
         <v>5.6760999999999999</v>
@@ -34597,9 +34266,9 @@
         <v>1.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B101">
         <v>3.4178000000000002</v>
@@ -34635,7 +34304,7 @@
         <v>0.12121334959999999</v>
       </c>
       <c r="O101" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P101">
         <v>5.6337999999999999</v>
@@ -34665,9 +34334,9 @@
         <v>-7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B102">
         <v>2.6903999999999999</v>
@@ -34703,7 +34372,7 @@
         <v>0.29347443519999999</v>
       </c>
       <c r="O102" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="P102">
         <v>3.9377499999999999</v>
